--- a/ig/DM-FEVRIER-2026/ValueSet-JDV-J89-CategorieProfessionnelle-RASS.xlsx
+++ b/ig/DM-FEVRIER-2026/ValueSet-JDV-J89-CategorieProfessionnelle-RASS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240329120000</t>
+    <t>20260223120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T12:00:00+01:00</t>
+    <t>2026-02-23T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -109,12 +109,6 @@
   </si>
   <si>
     <t>Etudiant</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Fonctionnaire d'Etat ou de collectivité locale</t>
   </si>
   <si>
     <t>M</t>
@@ -391,7 +385,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -435,23 +429,15 @@
         <v>34</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s" s="2">
         <v>36</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
